--- a/docs/data/jp/xlsx/446A.xlsx
+++ b/docs/data/jp/xlsx/446A.xlsx
@@ -228,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -350,6 +350,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -762,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC149"/>
+  <dimension ref="A1:AC155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4000,11 +4003,11 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 (2026.10.23)</t>
+          <t>현재 주가 (2026.10.26)</t>
         </is>
       </c>
       <c r="B47" s="29" t="n">
-        <v>2895</v>
+        <v>2880</v>
       </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
@@ -5241,7 +5244,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉 2026.10.23</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5457,227 +5460,267 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>3556</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>3891</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>4452</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>5084</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>3891</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>3290</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>3933</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>4404</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>4505</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>3933</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>1808</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>2101</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>2595</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>2548</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>2101</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>1482</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>1832</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>1809</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>1957</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>1832</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="K83" s="22" t="n">
-        <v>3</v>
+        <v>1808</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>0</v>
+        <v>2101</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>10</v>
+        <v>2595</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>0</v>
+        <v>2548</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>0</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>임대료 수익</t>
-        </is>
-      </c>
-      <c r="K84" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L84" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="X84" s="22" t="n">
-        <v>1</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>1482</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>1832</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>1809</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>1957</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>1832</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N85" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="X85" s="22" t="n">
-        <v>0</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>영업외수익 합계</t>
-        </is>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>2</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="K87" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N87" s="22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X87" s="22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>사채이자</t>
+          <t>임대료 수익</t>
         </is>
       </c>
       <c r="K88" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X88" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="K89" s="22" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L89" s="22" t="n">
         <v>0</v>
@@ -5686,7 +5729,7 @@
         <v>1</v>
       </c>
       <c r="N89" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X89" s="22" t="n">
         <v>0</v>
@@ -5695,933 +5738,947 @@
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용</t>
-        </is>
+          <t>영업외수익 합계</t>
+        </is>
+      </c>
+      <c r="K90" s="22" t="n">
+        <v>-1</v>
       </c>
       <c r="L90" s="22" t="n">
-        <v>48</v>
+        <v>2</v>
+      </c>
+      <c r="M90" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="N90" s="22" t="n">
+        <v>4</v>
       </c>
       <c r="X90" s="22" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="K91" s="22" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="L91" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M91" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="M91" s="22" t="n">
-        <v>0</v>
-      </c>
       <c r="N91" s="22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X91" s="22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>사채이자</t>
         </is>
       </c>
       <c r="K92" s="22" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L92" s="22" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M92" s="22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N92" s="22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X92" s="22" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="K93" s="12" t="n">
-        <v>1462</v>
-      </c>
-      <c r="L93" s="12" t="n">
-        <v>1781</v>
-      </c>
-      <c r="M93" s="12" t="n">
-        <v>1815</v>
-      </c>
-      <c r="N93" s="12" t="n">
-        <v>1958</v>
-      </c>
-      <c r="X93" s="12" t="n">
-        <v>1781</v>
+      <c r="A93" s="20" t="inlineStr">
+        <is>
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="K93" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="L93" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N93" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="X93" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각손실</t>
-        </is>
-      </c>
-      <c r="M94" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" s="22" t="n">
-        <v>2</v>
+          <t>상장 관련 비용</t>
+        </is>
+      </c>
+      <c r="L94" s="22" t="n">
+        <v>48</v>
+      </c>
+      <c r="X94" s="22" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>특별손실 합계</t>
-        </is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="K95" s="22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L95" s="22" t="n">
+        <v>2</v>
       </c>
       <c r="M95" s="22" t="n">
         <v>0</v>
       </c>
       <c r="N95" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" s="22" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="inlineStr">
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>영업외비용 합계</t>
+        </is>
+      </c>
+      <c r="K96" s="22" t="n">
+        <v>19</v>
+      </c>
+      <c r="L96" s="22" t="n">
+        <v>53</v>
+      </c>
+      <c r="M96" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="N96" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="X96" s="22" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="K97" s="12" t="n">
+        <v>1462</v>
+      </c>
+      <c r="L97" s="12" t="n">
+        <v>1781</v>
+      </c>
+      <c r="M97" s="12" t="n">
+        <v>1815</v>
+      </c>
+      <c r="N97" s="12" t="n">
+        <v>1958</v>
+      </c>
+      <c r="X97" s="12" t="n">
+        <v>1781</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="K98" s="17">
+        <f>IF(OR(K97="",G97=""),"",IF(G97&lt;=0,"",IFERROR(K97/G97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L98" s="17">
+        <f>IF(OR(L97="",H97=""),"",IF(H97&lt;=0,"",IFERROR(L97/H97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M98" s="17">
+        <f>IF(OR(M97="",I97=""),"",IF(I97&lt;=0,"",IFERROR(M97/I97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N98" s="17">
+        <f>IF(OR(N97="",J97=""),"",IF(J97&lt;=0,"",IFERROR(N97/J97-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X98" s="17">
+        <f>IF(OR(X97="",W97=""),"",IF(W97&lt;=0,"",IFERROR(X97/W97-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="20" t="inlineStr">
+        <is>
+          <t>고정자산 제각손실</t>
+        </is>
+      </c>
+      <c r="M99" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="M100" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="K96" s="12" t="n">
+      <c r="K101" s="12" t="n">
         <v>1462</v>
       </c>
-      <c r="L96" s="12" t="n">
+      <c r="L101" s="12" t="n">
         <v>1779</v>
       </c>
-      <c r="M96" s="12" t="n">
+      <c r="M101" s="12" t="n">
         <v>1815</v>
       </c>
-      <c r="N96" s="12" t="n">
+      <c r="N101" s="12" t="n">
         <v>1956</v>
       </c>
-      <c r="X96" s="12" t="n">
+      <c r="X101" s="12" t="n">
         <v>1779</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="20" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="20" t="inlineStr">
         <is>
           <t>법인세 등</t>
         </is>
       </c>
-      <c r="K97" s="22" t="n">
+      <c r="K102" s="22" t="n">
         <v>439</v>
       </c>
-      <c r="L97" s="22" t="n">
+      <c r="L102" s="22" t="n">
         <v>316</v>
       </c>
-      <c r="M97" s="22" t="n">
+      <c r="M102" s="22" t="n">
         <v>477</v>
       </c>
-      <c r="N97" s="22" t="n">
+      <c r="N102" s="22" t="n">
         <v>511</v>
       </c>
-      <c r="X97" s="22" t="n">
+      <c r="X102" s="22" t="n">
         <v>316</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="9" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="K98" s="12" t="n">
+      <c r="K103" s="12" t="n">
         <v>1023</v>
       </c>
-      <c r="L98" s="12" t="n">
+      <c r="L103" s="12" t="n">
         <v>1463</v>
       </c>
-      <c r="M98" s="12" t="n">
+      <c r="M103" s="12" t="n">
         <v>1337</v>
       </c>
-      <c r="N98" s="12" t="n">
+      <c r="N103" s="12" t="n">
         <v>1446</v>
       </c>
-      <c r="X98" s="12" t="n">
+      <c r="X103" s="12" t="n">
         <v>1463</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="18" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="K104" s="17">
+        <f>IF(OR(K103="",G103=""),"",IF(G103&lt;=0,"",IFERROR(K103/G103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L104" s="17">
+        <f>IF(OR(L103="",H103=""),"",IF(H103&lt;=0,"",IFERROR(L103/H103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M104" s="17">
+        <f>IF(OR(M103="",I103=""),"",IF(I103&lt;=0,"",IFERROR(M103/I103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N104" s="17">
+        <f>IF(OR(N103="",J103=""),"",IF(J103&lt;=0,"",IFERROR(N103/J103-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X104" s="17">
+        <f>IF(OR(X103="",W103=""),"",IF(W103&lt;=0,"",IFERROR(X103/W103-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B100" s="44" t="inlineStr">
+      <c r="B106" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C100" s="18" t="n"/>
-      <c r="D100" s="18" t="n"/>
-      <c r="E100" s="18" t="n"/>
-      <c r="F100" s="18" t="n"/>
-      <c r="G100" s="18" t="n"/>
-      <c r="H100" s="18" t="n"/>
-      <c r="I100" s="18" t="n"/>
-      <c r="J100" s="18" t="n"/>
-      <c r="K100" s="18" t="n"/>
-      <c r="L100" s="18" t="n"/>
-      <c r="M100" s="18" t="n"/>
-      <c r="N100" s="18" t="n"/>
-      <c r="O100" s="18" t="n"/>
-      <c r="P100" s="18" t="n"/>
-      <c r="Q100" s="18" t="n"/>
-      <c r="R100" s="18" t="n"/>
-      <c r="S100" s="18" t="n"/>
-      <c r="T100" s="18" t="n"/>
-      <c r="U100" s="18" t="n"/>
-      <c r="V100" s="18" t="n"/>
-      <c r="W100" s="18" t="n"/>
-      <c r="X100" s="18" t="n"/>
-      <c r="Y100" s="18" t="n"/>
-      <c r="Z100" s="18" t="n"/>
-      <c r="AA100" s="18" t="n"/>
-      <c r="AB100" s="18" t="n"/>
-      <c r="AC100" s="18" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="inlineStr">
+      <c r="C106" s="18" t="n"/>
+      <c r="D106" s="18" t="n"/>
+      <c r="E106" s="18" t="n"/>
+      <c r="F106" s="18" t="n"/>
+      <c r="G106" s="18" t="n"/>
+      <c r="H106" s="18" t="n"/>
+      <c r="I106" s="18" t="n"/>
+      <c r="J106" s="18" t="n"/>
+      <c r="K106" s="18" t="n"/>
+      <c r="L106" s="18" t="n"/>
+      <c r="M106" s="18" t="n"/>
+      <c r="N106" s="18" t="n"/>
+      <c r="O106" s="18" t="n"/>
+      <c r="P106" s="18" t="n"/>
+      <c r="Q106" s="18" t="n"/>
+      <c r="R106" s="18" t="n"/>
+      <c r="S106" s="18" t="n"/>
+      <c r="T106" s="18" t="n"/>
+      <c r="U106" s="18" t="n"/>
+      <c r="V106" s="18" t="n"/>
+      <c r="W106" s="18" t="n"/>
+      <c r="X106" s="18" t="n"/>
+      <c r="Y106" s="18" t="n"/>
+      <c r="Z106" s="18" t="n"/>
+      <c r="AA106" s="18" t="n"/>
+      <c r="AB106" s="18" t="n"/>
+      <c r="AC106" s="18" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B107" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C107" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="D101" s="5" t="inlineStr">
+      <c r="D107" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr">
+      <c r="E107" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="F101" s="5" t="inlineStr">
+      <c r="F107" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="G101" s="5" t="inlineStr">
+      <c r="G107" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="H101" s="5" t="inlineStr">
+      <c r="H107" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="I101" s="5" t="inlineStr">
+      <c r="I107" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="J101" s="5" t="inlineStr">
+      <c r="J107" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="K101" s="5" t="inlineStr">
+      <c r="K107" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="L101" s="5" t="inlineStr">
+      <c r="L107" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="M101" s="5" t="inlineStr">
+      <c r="M107" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="N101" s="5" t="inlineStr">
+      <c r="N107" s="5" t="inlineStr">
         <is>
           <t>2027.2Q</t>
         </is>
       </c>
-      <c r="O101" s="5" t="inlineStr">
+      <c r="O107" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P101" s="5" t="inlineStr">
+      <c r="P107" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q101" s="5" t="inlineStr">
+      <c r="Q107" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R101" s="5" t="inlineStr">
+      <c r="R107" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S101" s="5" t="inlineStr">
+      <c r="S107" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T101" s="5" t="inlineStr">
+      <c r="T107" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U101" s="5" t="inlineStr">
+      <c r="U107" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V101" s="5" t="inlineStr">
+      <c r="V107" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W101" s="5" t="inlineStr">
+      <c r="W107" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X101" s="5" t="inlineStr">
+      <c r="X107" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y101" s="5" t="inlineStr">
+      <c r="Y107" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z101" s="5" t="inlineStr">
+      <c r="Z107" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA101" s="5" t="inlineStr">
+      <c r="AA107" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB101" s="5" t="inlineStr">
+      <c r="AB107" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC101" s="5" t="inlineStr">
+      <c r="AC107" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="9" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="H102" s="12" t="n">
+      <c r="H108" s="12" t="n">
         <v>2799</v>
       </c>
-      <c r="J102" s="12" t="n">
+      <c r="J108" s="12" t="n">
         <v>2236</v>
       </c>
-      <c r="L102" s="12" t="n">
+      <c r="L108" s="12" t="n">
         <v>5477</v>
       </c>
-      <c r="N102" s="12" t="n">
+      <c r="N108" s="12" t="n">
         <v>3771</v>
       </c>
-      <c r="W102" s="12" t="n">
+      <c r="W108" s="12" t="n">
         <v>2799</v>
       </c>
-      <c r="X102" s="12" t="n">
+      <c r="X108" s="12" t="n">
         <v>5477</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비 및 기타 상각비</t>
-        </is>
-      </c>
-      <c r="H103" s="22" t="n">
-        <v>91</v>
-      </c>
-      <c r="J103" s="22" t="n">
-        <v>73</v>
-      </c>
-      <c r="L103" s="22" t="n">
-        <v>150</v>
-      </c>
-      <c r="N103" s="22" t="n">
-        <v>124</v>
-      </c>
-      <c r="W103" s="22" t="n">
-        <v>91</v>
-      </c>
-      <c r="X103" s="22" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="20" t="inlineStr">
-        <is>
-          <t>고정자산 매각이익</t>
-        </is>
-      </c>
-      <c r="H104" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="L104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W104" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="X104" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="20" t="inlineStr">
-        <is>
-          <t>고정자산 제각손실</t>
-        </is>
-      </c>
-      <c r="H105" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N105" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="W105" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X105" s="22" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="20" t="inlineStr">
-        <is>
-          <t>상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="H106" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="22" t="n">
-        <v>15</v>
-      </c>
-      <c r="L106" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="N106" s="22" t="n">
-        <v>-6</v>
-      </c>
-      <c r="W106" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X106" s="22" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="H107" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J107" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L107" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N107" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="W107" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="X107" s="22" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="20" t="inlineStr">
-        <is>
-          <t>관계회사 정리손실 충당금 증감</t>
-        </is>
-      </c>
-      <c r="H108" s="22" t="n">
-        <v>-244</v>
-      </c>
-      <c r="L108" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W108" s="22" t="n">
-        <v>-244</v>
-      </c>
-      <c r="X108" s="22" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>감가상각비 및 기타 상각비</t>
         </is>
       </c>
       <c r="H109" s="22" t="n">
-        <v>-0</v>
+        <v>91</v>
       </c>
       <c r="J109" s="22" t="n">
-        <v>-1</v>
+        <v>73</v>
       </c>
       <c r="L109" s="22" t="n">
-        <v>-4</v>
+        <v>150</v>
       </c>
       <c r="N109" s="22" t="n">
-        <v>-10</v>
+        <v>124</v>
       </c>
       <c r="W109" s="22" t="n">
-        <v>-0</v>
+        <v>91</v>
       </c>
       <c r="X109" s="22" t="n">
-        <v>-4</v>
+        <v>150</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
+          <t>고정자산 매각이익</t>
         </is>
       </c>
       <c r="H110" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="J110" s="22" t="n">
-        <v>6</v>
+        <v>-0</v>
       </c>
       <c r="L110" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="N110" s="22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W110" s="22" t="n">
-        <v>8</v>
+        <v>-0</v>
       </c>
       <c r="X110" s="22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용</t>
+          <t>고정자산 제각손실</t>
         </is>
       </c>
       <c r="H111" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="J111" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="L111" s="22" t="n">
-        <v>59</v>
+        <v>2</v>
+      </c>
+      <c r="N111" s="22" t="n">
+        <v>2</v>
       </c>
       <c r="W111" s="22" t="n">
         <v>0</v>
       </c>
       <c r="X111" s="22" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="20" t="inlineStr">
         <is>
-          <t>보조금 수입</t>
+          <t>상여충당금 증감</t>
         </is>
       </c>
       <c r="H112" s="22" t="n">
-        <v>-10</v>
+        <v>0</v>
+      </c>
+      <c r="J112" s="22" t="n">
+        <v>15</v>
       </c>
       <c r="L112" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="N112" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="W112" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="W112" s="22" t="n">
-        <v>-10</v>
-      </c>
       <c r="X112" s="22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="20" t="inlineStr">
         <is>
-          <t>보험환급금</t>
+          <t>대손충당금 증감</t>
         </is>
       </c>
       <c r="H113" s="22" t="n">
-        <v>-8</v>
+        <v>1</v>
+      </c>
+      <c r="J113" s="22" t="n">
+        <v>2</v>
       </c>
       <c r="L113" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="N113" s="22" t="n">
+        <v>2</v>
       </c>
       <c r="W113" s="22" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="X113" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
+          <t>관계회사 정리손실 충당금 증감</t>
         </is>
       </c>
       <c r="H114" s="22" t="n">
-        <v>-701</v>
-      </c>
-      <c r="J114" s="22" t="n">
-        <v>-515</v>
+        <v>-244</v>
       </c>
       <c r="L114" s="22" t="n">
-        <v>-1229</v>
-      </c>
-      <c r="N114" s="22" t="n">
-        <v>-832</v>
+        <v>0</v>
       </c>
       <c r="W114" s="22" t="n">
-        <v>-701</v>
+        <v>-244</v>
       </c>
       <c r="X114" s="22" t="n">
-        <v>-1229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="20" t="inlineStr">
         <is>
-          <t>선급비용 증감</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="H115" s="22" t="n">
-        <v>-52</v>
+        <v>-0</v>
+      </c>
+      <c r="J115" s="22" t="n">
+        <v>-1</v>
       </c>
       <c r="L115" s="22" t="n">
-        <v>-334</v>
+        <v>-4</v>
+      </c>
+      <c r="N115" s="22" t="n">
+        <v>-10</v>
       </c>
       <c r="W115" s="22" t="n">
-        <v>-52</v>
+        <v>-0</v>
       </c>
       <c r="X115" s="22" t="n">
-        <v>-334</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
+          <t>이자비용</t>
         </is>
       </c>
       <c r="H116" s="22" t="n">
-        <v>182</v>
+        <v>8</v>
       </c>
       <c r="J116" s="22" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="L116" s="22" t="n">
-        <v>172</v>
+        <v>11</v>
       </c>
       <c r="N116" s="22" t="n">
-        <v>112</v>
+        <v>5</v>
       </c>
       <c r="W116" s="22" t="n">
-        <v>182</v>
+        <v>8</v>
       </c>
       <c r="X116" s="22" t="n">
-        <v>172</v>
+        <v>11</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="20" t="inlineStr">
         <is>
-          <t>미지급금·미지급비용 증감</t>
+          <t>상장 관련 비용</t>
         </is>
       </c>
       <c r="H117" s="22" t="n">
-        <v>-157</v>
-      </c>
-      <c r="J117" s="22" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="L117" s="22" t="n">
-        <v>201</v>
-      </c>
-      <c r="N117" s="22" t="n">
-        <v>146</v>
+        <v>59</v>
       </c>
       <c r="W117" s="22" t="n">
-        <v>-157</v>
+        <v>0</v>
       </c>
       <c r="X117" s="22" t="n">
-        <v>201</v>
+        <v>59</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="20" t="inlineStr">
         <is>
-          <t>계약부채 증감</t>
+          <t>보조금 수입</t>
         </is>
       </c>
       <c r="H118" s="22" t="n">
-        <v>77</v>
+        <v>-10</v>
       </c>
       <c r="L118" s="22" t="n">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="W118" s="22" t="n">
-        <v>77</v>
+        <v>-10</v>
       </c>
       <c r="X118" s="22" t="n">
-        <v>294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="20" t="inlineStr">
         <is>
-          <t>예수금 증감</t>
+          <t>보험환급금</t>
         </is>
       </c>
       <c r="H119" s="22" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="L119" s="22" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="W119" s="22" t="n">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="X119" s="22" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="20" t="inlineStr">
         <is>
-          <t>미지급 소비세 증감</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="H120" s="22" t="n">
-        <v>273</v>
+        <v>-701</v>
+      </c>
+      <c r="J120" s="22" t="n">
+        <v>-515</v>
       </c>
       <c r="L120" s="22" t="n">
-        <v>301</v>
+        <v>-1229</v>
+      </c>
+      <c r="N120" s="22" t="n">
+        <v>-832</v>
       </c>
       <c r="W120" s="22" t="n">
-        <v>273</v>
+        <v>-701</v>
       </c>
       <c r="X120" s="22" t="n">
-        <v>301</v>
+        <v>-1229</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
-          <t>파산갱생채권 증감</t>
+          <t>선급비용 증감</t>
         </is>
       </c>
       <c r="H121" s="22" t="n">
-        <v>226</v>
+        <v>-52</v>
       </c>
       <c r="L121" s="22" t="n">
-        <v>0</v>
+        <v>-334</v>
       </c>
       <c r="W121" s="22" t="n">
-        <v>226</v>
+        <v>-52</v>
       </c>
       <c r="X121" s="22" t="n">
-        <v>0</v>
+        <v>-334</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="H122" s="22" t="n">
-        <v>-59</v>
+        <v>182</v>
       </c>
       <c r="J122" s="22" t="n">
-        <v>-169</v>
+        <v>68</v>
       </c>
       <c r="L122" s="22" t="n">
-        <v>56</v>
+        <v>172</v>
       </c>
       <c r="N122" s="22" t="n">
-        <v>-347</v>
+        <v>112</v>
       </c>
       <c r="W122" s="22" t="n">
-        <v>-59</v>
+        <v>182</v>
       </c>
       <c r="X122" s="22" t="n">
-        <v>56</v>
+        <v>172</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>미지급금·미지급비용 증감</t>
         </is>
       </c>
       <c r="H123" s="22" t="n">
-        <v>2424</v>
+        <v>-157</v>
       </c>
       <c r="J123" s="22" t="n">
-        <v>1798</v>
+        <v>83</v>
       </c>
       <c r="L123" s="22" t="n">
-        <v>5341</v>
+        <v>201</v>
       </c>
       <c r="N123" s="22" t="n">
-        <v>2969</v>
+        <v>146</v>
       </c>
       <c r="W123" s="22" t="n">
-        <v>2424</v>
+        <v>-157</v>
       </c>
       <c r="X123" s="22" t="n">
-        <v>5341</v>
+        <v>201</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="20" t="inlineStr">
         <is>
-          <t>이자 수취</t>
+          <t>계약부채 증감</t>
         </is>
       </c>
       <c r="H124" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="22" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="L124" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="N124" s="22" t="n">
-        <v>10</v>
+        <v>294</v>
       </c>
       <c r="W124" s="22" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="X124" s="22" t="n">
-        <v>4</v>
+        <v>294</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
+          <t>예수금 증감</t>
         </is>
       </c>
       <c r="H125" s="22" t="n">
-        <v>-9</v>
-      </c>
-      <c r="J125" s="22" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="L125" s="22" t="n">
-        <v>-11</v>
-      </c>
-      <c r="N125" s="22" t="n">
-        <v>-5</v>
+        <v>166</v>
       </c>
       <c r="W125" s="22" t="n">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="X125" s="22" t="n">
-        <v>-11</v>
+        <v>166</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="20" t="inlineStr">
         <is>
-          <t>보조금 수취</t>
+          <t>미지급 소비세 증감</t>
         </is>
       </c>
       <c r="H126" s="22" t="n">
-        <v>10</v>
+        <v>273</v>
       </c>
       <c r="L126" s="22" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="W126" s="22" t="n">
-        <v>10</v>
+        <v>273</v>
       </c>
       <c r="X126" s="22" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
         <is>
-          <t>보험금 수취</t>
+          <t>파산갱생채권 증감</t>
         </is>
       </c>
       <c r="H127" s="22" t="n">
-        <v>8</v>
+        <v>226</v>
       </c>
       <c r="L127" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W127" s="22" t="n">
-        <v>8</v>
+        <v>226</v>
       </c>
       <c r="X127" s="22" t="n">
         <v>0</v>
@@ -6630,496 +6687,634 @@
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부·환급</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="H128" s="22" t="n">
-        <v>-499</v>
+        <v>-59</v>
+      </c>
+      <c r="J128" s="22" t="n">
+        <v>-169</v>
       </c>
       <c r="L128" s="22" t="n">
-        <v>-1049</v>
+        <v>56</v>
+      </c>
+      <c r="N128" s="22" t="n">
+        <v>-347</v>
       </c>
       <c r="W128" s="22" t="n">
-        <v>-499</v>
+        <v>-59</v>
       </c>
       <c r="X128" s="22" t="n">
-        <v>-1049</v>
+        <v>56</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
-        </is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="H129" s="22" t="n">
+        <v>2424</v>
       </c>
       <c r="J129" s="22" t="n">
-        <v>-637</v>
+        <v>1798</v>
+      </c>
+      <c r="L129" s="22" t="n">
+        <v>5341</v>
       </c>
       <c r="N129" s="22" t="n">
-        <v>-1061</v>
+        <v>2969</v>
+      </c>
+      <c r="W129" s="22" t="n">
+        <v>2424</v>
+      </c>
+      <c r="X129" s="22" t="n">
+        <v>5341</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="H130" s="12" t="n">
-        <v>1934</v>
-      </c>
-      <c r="J130" s="12" t="n">
-        <v>1156</v>
-      </c>
-      <c r="L130" s="12" t="n">
-        <v>4286</v>
-      </c>
-      <c r="N130" s="12" t="n">
-        <v>1913</v>
-      </c>
-      <c r="W130" s="12" t="n">
-        <v>1934</v>
-      </c>
-      <c r="X130" s="12" t="n">
-        <v>4286</v>
+      <c r="A130" s="20" t="inlineStr">
+        <is>
+          <t>이자 수취</t>
+        </is>
+      </c>
+      <c r="H130" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L130" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N130" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="W130" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" s="22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>정기예금 예입</t>
+          <t>이자 지급</t>
         </is>
       </c>
       <c r="H131" s="22" t="n">
+        <v>-9</v>
+      </c>
+      <c r="J131" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L131" s="22" t="n">
+        <v>-11</v>
+      </c>
+      <c r="N131" s="22" t="n">
         <v>-5</v>
       </c>
-      <c r="J131" s="22" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L131" s="22" t="n">
-        <v>-5</v>
-      </c>
-      <c r="N131" s="22" t="n">
-        <v>-1005</v>
-      </c>
       <c r="W131" s="22" t="n">
-        <v>-5</v>
+        <v>-9</v>
       </c>
       <c r="X131" s="22" t="n">
-        <v>-5</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>정기예금 인출</t>
+          <t>보조금 수취</t>
         </is>
       </c>
       <c r="H132" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="J132" s="22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L132" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="N132" s="22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W132" s="22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="X132" s="22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>보험금 수취</t>
         </is>
       </c>
       <c r="H133" s="22" t="n">
-        <v>-197</v>
-      </c>
-      <c r="J133" s="22" t="n">
-        <v>-17</v>
+        <v>8</v>
       </c>
       <c r="L133" s="22" t="n">
-        <v>-33</v>
-      </c>
-      <c r="N133" s="22" t="n">
-        <v>-198</v>
+        <v>0</v>
       </c>
       <c r="W133" s="22" t="n">
-        <v>-197</v>
+        <v>8</v>
       </c>
       <c r="X133" s="22" t="n">
-        <v>-33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
+          <t>법인세 납부·환급</t>
         </is>
       </c>
       <c r="H134" s="22" t="n">
-        <v>1</v>
+        <v>-499</v>
       </c>
       <c r="L134" s="22" t="n">
-        <v>0</v>
+        <v>-1049</v>
       </c>
       <c r="W134" s="22" t="n">
-        <v>1</v>
+        <v>-499</v>
       </c>
       <c r="X134" s="22" t="n">
-        <v>0</v>
+        <v>-1049</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>유형자산 제각 지출</t>
-        </is>
-      </c>
-      <c r="H135" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" s="22" t="n">
-        <v>-0</v>
-      </c>
-      <c r="W135" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X135" s="22" t="n">
-        <v>-0</v>
+          <t>법인세 납부</t>
+        </is>
+      </c>
+      <c r="J135" s="22" t="n">
+        <v>-637</v>
+      </c>
+      <c r="N135" s="22" t="n">
+        <v>-1061</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="20" t="inlineStr">
-        <is>
-          <t>임차보증금·보증금 납입</t>
-        </is>
-      </c>
-      <c r="H136" s="22" t="n">
-        <v>-206</v>
-      </c>
-      <c r="J136" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" s="22" t="n">
-        <v>-1852</v>
-      </c>
-      <c r="N136" s="22" t="n">
-        <v>-1776</v>
-      </c>
-      <c r="W136" s="22" t="n">
-        <v>-206</v>
-      </c>
-      <c r="X136" s="22" t="n">
-        <v>-1852</v>
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="H136" s="12" t="n">
+        <v>1934</v>
+      </c>
+      <c r="J136" s="12" t="n">
+        <v>1156</v>
+      </c>
+      <c r="L136" s="12" t="n">
+        <v>4286</v>
+      </c>
+      <c r="N136" s="12" t="n">
+        <v>1913</v>
+      </c>
+      <c r="W136" s="12" t="n">
+        <v>1934</v>
+      </c>
+      <c r="X136" s="12" t="n">
+        <v>4286</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>임차보증금·보증금 회수</t>
+          <t>정기예금 예입</t>
         </is>
       </c>
       <c r="H137" s="22" t="n">
-        <v>0</v>
+        <v>-5</v>
+      </c>
+      <c r="J137" s="22" t="n">
+        <v>-5</v>
       </c>
       <c r="L137" s="22" t="n">
-        <v>15</v>
+        <v>-5</v>
+      </c>
+      <c r="N137" s="22" t="n">
+        <v>-1005</v>
       </c>
       <c r="W137" s="22" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="X137" s="22" t="n">
-        <v>15</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>정기예금 인출</t>
         </is>
       </c>
       <c r="H138" s="22" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="J138" s="22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L138" s="22" t="n">
-        <v>-0</v>
+        <v>5</v>
       </c>
       <c r="N138" s="22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W138" s="22" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="X138" s="22" t="n">
-        <v>-0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="H139" s="12" t="n">
-        <v>-379</v>
-      </c>
-      <c r="J139" s="12" t="n">
-        <v>-15</v>
-      </c>
-      <c r="L139" s="12" t="n">
-        <v>-1871</v>
-      </c>
-      <c r="N139" s="12" t="n">
-        <v>-2974</v>
-      </c>
-      <c r="W139" s="12" t="n">
-        <v>-379</v>
-      </c>
-      <c r="X139" s="12" t="n">
-        <v>-1871</v>
+      <c r="A139" s="20" t="inlineStr">
+        <is>
+          <t>유형자산 취득(설비투자)</t>
+        </is>
+      </c>
+      <c r="H139" s="22" t="n">
+        <v>-197</v>
+      </c>
+      <c r="J139" s="22" t="n">
+        <v>-17</v>
+      </c>
+      <c r="L139" s="22" t="n">
+        <v>-33</v>
+      </c>
+      <c r="N139" s="22" t="n">
+        <v>-198</v>
+      </c>
+      <c r="W139" s="22" t="n">
+        <v>-197</v>
+      </c>
+      <c r="X139" s="22" t="n">
+        <v>-33</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>단기차입</t>
+          <t>유형자산 매각</t>
         </is>
       </c>
       <c r="H140" s="22" t="n">
-        <v>690</v>
-      </c>
-      <c r="J140" s="22" t="n">
-        <v>600</v>
+        <v>1</v>
       </c>
       <c r="L140" s="22" t="n">
-        <v>600</v>
-      </c>
-      <c r="N140" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W140" s="22" t="n">
-        <v>690</v>
+        <v>1</v>
       </c>
       <c r="X140" s="22" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>단기차입금 상환</t>
+          <t>유형자산 제각 지출</t>
         </is>
       </c>
       <c r="H141" s="22" t="n">
-        <v>-656</v>
-      </c>
-      <c r="J141" s="22" t="n">
-        <v>-463</v>
+        <v>0</v>
       </c>
       <c r="L141" s="22" t="n">
-        <v>-663</v>
-      </c>
-      <c r="N141" s="22" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W141" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="W141" s="22" t="n">
-        <v>-656</v>
-      </c>
       <c r="X141" s="22" t="n">
-        <v>-663</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>장기차입</t>
+          <t>임차보증금·보증금 납입</t>
         </is>
       </c>
       <c r="H142" s="22" t="n">
-        <v>435</v>
+        <v>-206</v>
+      </c>
+      <c r="J142" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="L142" s="22" t="n">
-        <v>0</v>
+        <v>-1852</v>
+      </c>
+      <c r="N142" s="22" t="n">
+        <v>-1776</v>
       </c>
       <c r="W142" s="22" t="n">
-        <v>435</v>
+        <v>-206</v>
       </c>
       <c r="X142" s="22" t="n">
-        <v>0</v>
+        <v>-1852</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>장기차입금 상환</t>
+          <t>임차보증금·보증금 회수</t>
         </is>
       </c>
       <c r="H143" s="22" t="n">
-        <v>-243</v>
-      </c>
-      <c r="J143" s="22" t="n">
-        <v>-114</v>
+        <v>0</v>
       </c>
       <c r="L143" s="22" t="n">
-        <v>-233</v>
-      </c>
-      <c r="N143" s="22" t="n">
-        <v>-121</v>
+        <v>15</v>
       </c>
       <c r="W143" s="22" t="n">
-        <v>-243</v>
+        <v>0</v>
       </c>
       <c r="X143" s="22" t="n">
-        <v>-233</v>
+        <v>15</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>사채 상환</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="H144" s="22" t="n">
-        <v>-91</v>
+        <v>23</v>
       </c>
       <c r="J144" s="22" t="n">
-        <v>-43</v>
+        <v>1</v>
       </c>
       <c r="L144" s="22" t="n">
-        <v>-86</v>
+        <v>-0</v>
       </c>
       <c r="N144" s="22" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="W144" s="22" t="n">
-        <v>-91</v>
+        <v>23</v>
       </c>
       <c r="X144" s="22" t="n">
-        <v>-86</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="20" t="inlineStr">
-        <is>
-          <t>주식 발행</t>
-        </is>
-      </c>
-      <c r="H145" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" s="22" t="n">
-        <v>9374</v>
-      </c>
-      <c r="W145" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X145" s="22" t="n">
-        <v>9374</v>
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="H145" s="12" t="n">
+        <v>-379</v>
+      </c>
+      <c r="J145" s="12" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L145" s="12" t="n">
+        <v>-1871</v>
+      </c>
+      <c r="N145" s="12" t="n">
+        <v>-2974</v>
+      </c>
+      <c r="W145" s="12" t="n">
+        <v>-379</v>
+      </c>
+      <c r="X145" s="12" t="n">
+        <v>-1871</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>상장 관련 비용 지출</t>
+          <t>단기차입</t>
         </is>
       </c>
       <c r="H146" s="22" t="n">
+        <v>690</v>
+      </c>
+      <c r="J146" s="22" t="n">
+        <v>600</v>
+      </c>
+      <c r="L146" s="22" t="n">
+        <v>600</v>
+      </c>
+      <c r="N146" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="L146" s="22" t="n">
-        <v>-59</v>
-      </c>
       <c r="W146" s="22" t="n">
-        <v>0</v>
+        <v>690</v>
       </c>
       <c r="X146" s="22" t="n">
-        <v>-59</v>
+        <v>600</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>단기차입금 상환</t>
         </is>
       </c>
       <c r="H147" s="22" t="n">
-        <v>-6</v>
+        <v>-656</v>
       </c>
       <c r="J147" s="22" t="n">
-        <v>-9</v>
+        <v>-463</v>
       </c>
       <c r="L147" s="22" t="n">
-        <v>-19</v>
+        <v>-663</v>
       </c>
       <c r="N147" s="22" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="W147" s="22" t="n">
-        <v>-6</v>
+        <v>-656</v>
       </c>
       <c r="X147" s="22" t="n">
-        <v>-19</v>
+        <v>-663</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="H148" s="12" t="n">
-        <v>127</v>
-      </c>
-      <c r="J148" s="12" t="n">
-        <v>-29</v>
-      </c>
-      <c r="L148" s="12" t="n">
-        <v>8912</v>
-      </c>
-      <c r="N148" s="12" t="n">
-        <v>-146</v>
-      </c>
-      <c r="W148" s="12" t="n">
-        <v>127</v>
-      </c>
-      <c r="X148" s="12" t="n">
-        <v>8912</v>
+      <c r="A148" s="20" t="inlineStr">
+        <is>
+          <t>장기차입</t>
+        </is>
+      </c>
+      <c r="H148" s="22" t="n">
+        <v>435</v>
+      </c>
+      <c r="L148" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W148" s="22" t="n">
+        <v>435</v>
+      </c>
+      <c r="X148" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
+          <t>장기차입금 상환</t>
+        </is>
+      </c>
+      <c r="H149" s="22" t="n">
+        <v>-243</v>
+      </c>
+      <c r="J149" s="22" t="n">
+        <v>-114</v>
+      </c>
+      <c r="L149" s="22" t="n">
+        <v>-233</v>
+      </c>
+      <c r="N149" s="22" t="n">
+        <v>-121</v>
+      </c>
+      <c r="W149" s="22" t="n">
+        <v>-243</v>
+      </c>
+      <c r="X149" s="22" t="n">
+        <v>-233</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="20" t="inlineStr">
+        <is>
+          <t>사채 상환</t>
+        </is>
+      </c>
+      <c r="H150" s="22" t="n">
+        <v>-91</v>
+      </c>
+      <c r="J150" s="22" t="n">
+        <v>-43</v>
+      </c>
+      <c r="L150" s="22" t="n">
+        <v>-86</v>
+      </c>
+      <c r="N150" s="22" t="n">
+        <v>-10</v>
+      </c>
+      <c r="W150" s="22" t="n">
+        <v>-91</v>
+      </c>
+      <c r="X150" s="22" t="n">
+        <v>-86</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="20" t="inlineStr">
+        <is>
+          <t>주식 발행</t>
+        </is>
+      </c>
+      <c r="H151" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" s="22" t="n">
+        <v>9374</v>
+      </c>
+      <c r="W151" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X151" s="22" t="n">
+        <v>9374</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="20" t="inlineStr">
+        <is>
+          <t>상장 관련 비용 지출</t>
+        </is>
+      </c>
+      <c r="H152" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" s="22" t="n">
+        <v>-59</v>
+      </c>
+      <c r="W152" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X152" s="22" t="n">
+        <v>-59</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="H153" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J153" s="22" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L153" s="22" t="n">
+        <v>-19</v>
+      </c>
+      <c r="N153" s="22" t="n">
+        <v>-15</v>
+      </c>
+      <c r="W153" s="22" t="n">
+        <v>-6</v>
+      </c>
+      <c r="X153" s="22" t="n">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="H154" s="12" t="n">
+        <v>127</v>
+      </c>
+      <c r="J154" s="12" t="n">
+        <v>-29</v>
+      </c>
+      <c r="L154" s="12" t="n">
+        <v>8912</v>
+      </c>
+      <c r="N154" s="12" t="n">
+        <v>-146</v>
+      </c>
+      <c r="W154" s="12" t="n">
+        <v>127</v>
+      </c>
+      <c r="X154" s="12" t="n">
+        <v>8912</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="20" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="H149" s="22" t="n">
+      <c r="H155" s="22" t="n">
         <v>1681</v>
       </c>
-      <c r="J149" s="22" t="n">
+      <c r="J155" s="22" t="n">
         <v>1110</v>
       </c>
-      <c r="L149" s="22" t="n">
+      <c r="L155" s="22" t="n">
         <v>11326</v>
       </c>
-      <c r="N149" s="22" t="n">
+      <c r="N155" s="22" t="n">
         <v>-1207</v>
       </c>
-      <c r="W149" s="22" t="n">
+      <c r="W155" s="22" t="n">
         <v>1681</v>
       </c>
-      <c r="X149" s="22" t="n">
+      <c r="X155" s="22" t="n">
         <v>11326</v>
       </c>
     </row>
@@ -7157,7 +7352,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -8212,7 +8407,7 @@
       <c r="I42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -8252,7 +8447,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -8292,7 +8487,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -8332,7 +8527,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -8372,7 +8567,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -8412,7 +8607,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -8452,7 +8647,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -8462,31 +8657,31 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",H28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",I28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -8507,7 +8702,7 @@
       <c r="I50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -8547,7 +8742,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -8587,7 +8782,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -8627,7 +8822,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -8667,7 +8862,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -8707,7 +8902,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -8762,7 +8957,7 @@
       <c r="I57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -8802,7 +8997,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -8812,37 +9007,37 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -8852,37 +9047,37 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -8892,37 +9087,37 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -8932,31 +9127,31 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
@@ -8977,7 +9172,7 @@
       <c r="I63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -9017,7 +9212,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -9057,7 +9252,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -9097,7 +9292,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -10382,1406 +10577,1406 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>노스샌드 섹터·사업 데이터</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="52" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>2단계 보고서를 만들 때 모은 자료 · 월차 · 출처는 맨 오른쪽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>상반기 fy27</t>
         </is>
       </c>
-      <c r="B4" s="53" t="n"/>
-      <c r="C4" s="53" t="n"/>
-      <c r="D4" s="53" t="n"/>
-      <c r="E4" s="53" t="n"/>
-      <c r="F4" s="53" t="n"/>
-      <c r="G4" s="53" t="n"/>
-      <c r="H4" s="53" t="n"/>
-      <c r="I4" s="53" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
+      <c r="E4" s="54" t="n"/>
+      <c r="F4" s="54" t="n"/>
+      <c r="G4" s="54" t="n"/>
+      <c r="H4" s="54" t="n"/>
+      <c r="I4" s="54" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="54" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="I5" s="54" t="inlineStr">
+      <c r="I5" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="A6" s="56" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B6" s="56" t="n">
+      <c r="B6" s="57" t="n">
         <v>184.45</v>
       </c>
-      <c r="I6" s="57" t="inlineStr">
+      <c r="I6" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="55" t="inlineStr">
+      <c r="A7" s="56" t="inlineStr">
         <is>
           <t>YoY 매출</t>
         </is>
       </c>
-      <c r="B7" s="56" t="n">
+      <c r="B7" s="57" t="n">
         <v>60.2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="55" t="inlineStr">
+      <c r="A8" s="56" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
       </c>
-      <c r="B8" s="56" t="n">
+      <c r="B8" s="57" t="n">
         <v>37.66</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="55" t="inlineStr">
+      <c r="A9" s="56" t="inlineStr">
         <is>
           <t>YoY 영업이익</t>
         </is>
       </c>
-      <c r="B9" s="56" t="n">
+      <c r="B9" s="57" t="n">
         <v>68.7</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="A10" s="56" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="B10" s="56" t="n">
+      <c r="B10" s="57" t="n">
         <v>27.83</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="55" t="inlineStr">
+      <c r="A11" s="56" t="inlineStr">
         <is>
           <t>YoY 순이익</t>
         </is>
       </c>
-      <c r="B11" s="56" t="n">
+      <c r="B11" s="57" t="n">
         <v>78.3</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="55" t="inlineStr">
+      <c r="A12" s="56" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="B12" s="56" t="n">
+      <c r="B12" s="57" t="n">
         <v>40.33</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="53" t="inlineStr">
+      <c r="A14" s="54" t="inlineStr">
         <is>
           <t>bs 2q</t>
         </is>
       </c>
-      <c r="B14" s="53" t="n"/>
-      <c r="C14" s="53" t="n"/>
-      <c r="D14" s="53" t="n"/>
-      <c r="E14" s="53" t="n"/>
-      <c r="F14" s="53" t="n"/>
-      <c r="G14" s="53" t="n"/>
-      <c r="H14" s="53" t="n"/>
-      <c r="I14" s="53" t="n"/>
+      <c r="B14" s="54" t="n"/>
+      <c r="C14" s="54" t="n"/>
+      <c r="D14" s="54" t="n"/>
+      <c r="E14" s="54" t="n"/>
+      <c r="F14" s="54" t="n"/>
+      <c r="G14" s="54" t="n"/>
+      <c r="H14" s="54" t="n"/>
+      <c r="I14" s="54" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="54" t="inlineStr">
+      <c r="A15" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B15" s="54" t="inlineStr">
+      <c r="B15" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="I15" s="54" t="inlineStr">
+      <c r="I15" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="55" t="inlineStr">
+      <c r="A16" s="56" t="inlineStr">
         <is>
           <t>합계 assets</t>
         </is>
       </c>
-      <c r="B16" s="56" t="n">
+      <c r="B16" s="57" t="n">
         <v>243.76</v>
       </c>
-      <c r="I16" s="57" t="inlineStr">
+      <c r="I16" s="58" t="inlineStr">
         <is>
           <t>FY26 재무활동 +89.12억 = 상장 공모 자금</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="55" t="inlineStr">
+      <c r="A17" s="56" t="inlineStr">
         <is>
           <t>equity</t>
         </is>
       </c>
-      <c r="B17" s="56" t="n">
+      <c r="B17" s="57" t="n">
         <v>192.38</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="55" t="inlineStr">
+      <c r="A18" s="56" t="inlineStr">
         <is>
           <t>equity ratio</t>
         </is>
       </c>
-      <c r="B18" s="56" t="n">
+      <c r="B18" s="57" t="n">
         <v>78.90000000000001</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="55" t="inlineStr">
+      <c r="A19" s="56" t="inlineStr">
         <is>
           <t>cash fy26 end</t>
         </is>
       </c>
-      <c r="B19" s="56" t="n">
+      <c r="B19" s="57" t="n">
         <v>145.97</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="55" t="inlineStr">
+      <c r="A20" s="56" t="inlineStr">
         <is>
           <t>cfo fy26</t>
         </is>
       </c>
-      <c r="B20" s="56" t="n">
+      <c r="B20" s="57" t="n">
         <v>42.86</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="53" t="inlineStr">
+      <c r="A22" s="54" t="inlineStr">
         <is>
           <t>가이던스 implied 하반기 fy2027</t>
         </is>
       </c>
-      <c r="B22" s="53" t="n"/>
-      <c r="C22" s="53" t="n"/>
-      <c r="D22" s="53" t="n"/>
-      <c r="E22" s="53" t="n"/>
-      <c r="F22" s="53" t="n"/>
-      <c r="G22" s="53" t="n"/>
-      <c r="H22" s="53" t="n"/>
-      <c r="I22" s="53" t="n"/>
+      <c r="B22" s="54" t="n"/>
+      <c r="C22" s="54" t="n"/>
+      <c r="D22" s="54" t="n"/>
+      <c r="E22" s="54" t="n"/>
+      <c r="F22" s="54" t="n"/>
+      <c r="G22" s="54" t="n"/>
+      <c r="H22" s="54" t="n"/>
+      <c r="I22" s="54" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="54" t="inlineStr">
+      <c r="A23" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B23" s="54" t="inlineStr">
+      <c r="B23" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="I23" s="54" t="inlineStr">
+      <c r="I23" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="55" t="inlineStr">
+      <c r="A24" s="56" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B24" s="56" t="n">
+      <c r="B24" s="57" t="n">
         <v>221.15</v>
       </c>
-      <c r="I24" s="57" t="inlineStr">
+      <c r="I24" s="58" t="inlineStr">
         <is>
           <t>연간 가이던스 − 상반기(계산), 3Q+4Q 평균 매출 110.6억/분기</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="55" t="inlineStr">
+      <c r="A25" s="56" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
       </c>
-      <c r="B25" s="56" t="n">
+      <c r="B25" s="57" t="n">
         <v>54.41</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="53" t="inlineStr">
+      <c r="A27" s="54" t="inlineStr">
         <is>
           <t>컨센서스 · FY2027</t>
         </is>
       </c>
-      <c r="B27" s="53" t="n"/>
-      <c r="C27" s="53" t="n"/>
-      <c r="D27" s="53" t="n"/>
-      <c r="E27" s="53" t="n"/>
-      <c r="F27" s="53" t="n"/>
-      <c r="G27" s="53" t="n"/>
-      <c r="H27" s="53" t="n"/>
-      <c r="I27" s="53" t="n"/>
+      <c r="B27" s="54" t="n"/>
+      <c r="C27" s="54" t="n"/>
+      <c r="D27" s="54" t="n"/>
+      <c r="E27" s="54" t="n"/>
+      <c r="F27" s="54" t="n"/>
+      <c r="G27" s="54" t="n"/>
+      <c r="H27" s="54" t="n"/>
+      <c r="I27" s="54" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="54" t="inlineStr">
+      <c r="A28" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B28" s="54" t="inlineStr">
+      <c r="B28" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="I28" s="54" t="inlineStr">
+      <c r="I28" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="55" t="inlineStr">
+      <c r="A29" s="56" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B29" s="56" t="n">
+      <c r="B29" s="57" t="n">
         <v>407</v>
       </c>
-      <c r="I29" s="57" t="inlineStr">
+      <c r="I29" s="58" t="inlineStr">
         <is>
           <t>야후 파이낸스 26.10.23, 애널리스트 2명(시장 컨센서스 아님)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="55" t="inlineStr">
+      <c r="A30" s="56" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="B30" s="56" t="n">
+      <c r="B30" s="57" t="n">
         <v>100.65</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="55" t="inlineStr">
+      <c r="A31" s="56" t="inlineStr">
         <is>
           <t>EPS 30d ago</t>
         </is>
       </c>
-      <c r="B31" s="56" t="n">
+      <c r="B31" s="57" t="n">
         <v>92.7</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="53" t="inlineStr">
+      <c r="A33" s="54" t="inlineStr">
         <is>
           <t>컨센서스 · FY2028</t>
         </is>
       </c>
-      <c r="B33" s="53" t="n"/>
-      <c r="C33" s="53" t="n"/>
-      <c r="D33" s="53" t="n"/>
-      <c r="E33" s="53" t="n"/>
-      <c r="F33" s="53" t="n"/>
-      <c r="G33" s="53" t="n"/>
-      <c r="H33" s="53" t="n"/>
-      <c r="I33" s="53" t="n"/>
+      <c r="B33" s="54" t="n"/>
+      <c r="C33" s="54" t="n"/>
+      <c r="D33" s="54" t="n"/>
+      <c r="E33" s="54" t="n"/>
+      <c r="F33" s="54" t="n"/>
+      <c r="G33" s="54" t="n"/>
+      <c r="H33" s="54" t="n"/>
+      <c r="I33" s="54" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="54" t="inlineStr">
+      <c r="A34" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B34" s="54" t="inlineStr">
+      <c r="B34" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="I34" s="54" t="inlineStr">
+      <c r="I34" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="55" t="inlineStr">
+      <c r="A35" s="56" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B35" s="56" t="n">
+      <c r="B35" s="57" t="n">
         <v>571.5</v>
       </c>
-      <c r="I35" s="57" t="inlineStr">
+      <c r="I35" s="58" t="inlineStr">
         <is>
           <t>야후 파이낸스 26.10.23, 애널리스트 2명(시장 컨센서스 아님)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="55" t="inlineStr">
+      <c r="A36" s="56" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="B36" s="56" t="n">
+      <c r="B36" s="57" t="n">
         <v>143.3</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="55" t="inlineStr">
+      <c r="A37" s="56" t="inlineStr">
         <is>
           <t>EPS 30d ago</t>
         </is>
       </c>
-      <c r="B37" s="56" t="n">
+      <c r="B37" s="57" t="n">
         <v>126.9</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="53" t="inlineStr">
+      <c r="A39" s="54" t="inlineStr">
         <is>
           <t>컨센서스 · 목표주가 가격</t>
         </is>
       </c>
-      <c r="B39" s="53" t="n"/>
-      <c r="C39" s="53" t="n"/>
-      <c r="D39" s="53" t="n"/>
-      <c r="E39" s="53" t="n"/>
-      <c r="F39" s="53" t="n"/>
-      <c r="G39" s="53" t="n"/>
-      <c r="H39" s="53" t="n"/>
-      <c r="I39" s="53" t="n"/>
+      <c r="B39" s="54" t="n"/>
+      <c r="C39" s="54" t="n"/>
+      <c r="D39" s="54" t="n"/>
+      <c r="E39" s="54" t="n"/>
+      <c r="F39" s="54" t="n"/>
+      <c r="G39" s="54" t="n"/>
+      <c r="H39" s="54" t="n"/>
+      <c r="I39" s="54" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="54" t="inlineStr">
+      <c r="A40" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B40" s="54" t="inlineStr">
+      <c r="B40" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="I40" s="54" t="inlineStr">
+      <c r="I40" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="55" t="inlineStr">
+      <c r="A41" s="56" t="inlineStr">
         <is>
           <t>평균</t>
         </is>
       </c>
-      <c r="B41" s="58" t="n">
+      <c r="B41" s="59" t="n">
         <v>3200</v>
       </c>
-      <c r="I41" s="57" t="inlineStr">
+      <c r="I41" s="58" t="inlineStr">
         <is>
           <t>야후 파이낸스 26.10.23, 애널리스트 2명(시장 컨센서스 아님)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="55" t="inlineStr">
+      <c r="A42" s="56" t="inlineStr">
         <is>
           <t>애널리스트 수</t>
         </is>
       </c>
-      <c r="B42" s="58" t="n">
+      <c r="B42" s="59" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="53" t="inlineStr">
+      <c r="A44" s="54" t="inlineStr">
         <is>
           <t>밸류에이션 now</t>
         </is>
       </c>
-      <c r="B44" s="53" t="n"/>
-      <c r="C44" s="53" t="n"/>
-      <c r="D44" s="53" t="n"/>
-      <c r="E44" s="53" t="n"/>
-      <c r="F44" s="53" t="n"/>
-      <c r="G44" s="53" t="n"/>
-      <c r="H44" s="53" t="n"/>
-      <c r="I44" s="53" t="n"/>
+      <c r="B44" s="54" t="n"/>
+      <c r="C44" s="54" t="n"/>
+      <c r="D44" s="54" t="n"/>
+      <c r="E44" s="54" t="n"/>
+      <c r="F44" s="54" t="n"/>
+      <c r="G44" s="54" t="n"/>
+      <c r="H44" s="54" t="n"/>
+      <c r="I44" s="54" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="54" t="inlineStr">
+      <c r="A45" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B45" s="54" t="inlineStr">
+      <c r="B45" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="I45" s="54" t="inlineStr">
+      <c r="I45" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="55" t="inlineStr">
+      <c r="A46" s="56" t="inlineStr">
         <is>
           <t>PER 가이던스</t>
         </is>
       </c>
-      <c r="B46" s="56" t="n">
+      <c r="B46" s="57" t="n">
         <v>29.3</v>
       </c>
-      <c r="I46" s="57" t="inlineStr">
+      <c r="I46" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="55" t="inlineStr">
+      <c r="A47" s="56" t="inlineStr">
         <is>
           <t>PER cons fy28</t>
         </is>
       </c>
-      <c r="B47" s="56" t="n">
+      <c r="B47" s="57" t="n">
         <v>20.2</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="55" t="inlineStr">
+      <c r="A48" s="56" t="inlineStr">
         <is>
           <t>trailing PER yahoo</t>
         </is>
       </c>
-      <c r="B48" s="56" t="n">
+      <c r="B48" s="57" t="n">
         <v>39.7</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="55" t="inlineStr">
+      <c r="A49" s="56" t="inlineStr">
         <is>
           <t>PBR approx</t>
         </is>
       </c>
-      <c r="B49" s="56" t="n">
+      <c r="B49" s="57" t="n">
         <v>10.4</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="53" t="inlineStr">
+      <c r="A51" s="54" t="inlineStr">
         <is>
           <t>stock range · chg</t>
         </is>
       </c>
-      <c r="B51" s="53" t="n"/>
-      <c r="C51" s="53" t="n"/>
-      <c r="D51" s="53" t="n"/>
-      <c r="E51" s="53" t="n"/>
-      <c r="F51" s="53" t="n"/>
-      <c r="G51" s="53" t="n"/>
-      <c r="H51" s="53" t="n"/>
-      <c r="I51" s="53" t="n"/>
+      <c r="B51" s="54" t="n"/>
+      <c r="C51" s="54" t="n"/>
+      <c r="D51" s="54" t="n"/>
+      <c r="E51" s="54" t="n"/>
+      <c r="F51" s="54" t="n"/>
+      <c r="G51" s="54" t="n"/>
+      <c r="H51" s="54" t="n"/>
+      <c r="I51" s="54" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="54" t="inlineStr">
+      <c r="A52" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B52" s="54" t="inlineStr">
+      <c r="B52" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="I52" s="54" t="inlineStr">
+      <c r="I52" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="55" t="inlineStr">
+      <c r="A53" s="56" t="inlineStr">
         <is>
           <t>1w</t>
         </is>
       </c>
-      <c r="B53" s="56" t="n">
+      <c r="B53" s="57" t="n">
         <v>8</v>
       </c>
-      <c r="I53" s="57" t="inlineStr">
+      <c r="I53" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="55" t="inlineStr">
+      <c r="A54" s="56" t="inlineStr">
         <is>
           <t>1m</t>
         </is>
       </c>
-      <c r="B54" s="56" t="n">
+      <c r="B54" s="57" t="n">
         <v>25.4</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="55" t="inlineStr">
+      <c r="A55" s="56" t="inlineStr">
         <is>
           <t>3m</t>
         </is>
       </c>
-      <c r="B55" s="56" t="n">
+      <c r="B55" s="57" t="n">
         <v>99.7</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="55" t="inlineStr">
+      <c r="A56" s="56" t="inlineStr">
         <is>
           <t>6m</t>
         </is>
       </c>
-      <c r="B56" s="56" t="n">
+      <c r="B56" s="57" t="n">
         <v>112.1</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="55" t="inlineStr">
+      <c r="A57" s="56" t="inlineStr">
         <is>
           <t>ytd</t>
         </is>
       </c>
-      <c r="B57" s="56" t="n">
+      <c r="B57" s="57" t="n">
         <v>62.5</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="55" t="inlineStr">
+      <c r="A58" s="56" t="inlineStr">
         <is>
           <t>since first</t>
         </is>
       </c>
-      <c r="B58" s="56" t="n">
+      <c r="B58" s="57" t="n">
         <v>97.3</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="53" t="inlineStr">
+      <c r="A60" s="54" t="inlineStr">
         <is>
           <t>peers · 6532 베이커런트(2월 결산, IFRS)</t>
         </is>
       </c>
-      <c r="B60" s="53" t="n"/>
-      <c r="C60" s="53" t="n"/>
-      <c r="D60" s="53" t="n"/>
-      <c r="E60" s="53" t="n"/>
-      <c r="F60" s="53" t="n"/>
-      <c r="G60" s="53" t="n"/>
-      <c r="H60" s="53" t="n"/>
-      <c r="I60" s="53" t="n"/>
+      <c r="B60" s="54" t="n"/>
+      <c r="C60" s="54" t="n"/>
+      <c r="D60" s="54" t="n"/>
+      <c r="E60" s="54" t="n"/>
+      <c r="F60" s="54" t="n"/>
+      <c r="G60" s="54" t="n"/>
+      <c r="H60" s="54" t="n"/>
+      <c r="I60" s="54" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="54" t="inlineStr">
+      <c r="A61" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B61" s="54" t="inlineStr">
+      <c r="B61" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="I61" s="54" t="inlineStr">
+      <c r="I61" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="55" t="inlineStr">
+      <c r="A62" s="56" t="inlineStr">
         <is>
           <t>cons FY27 EPS</t>
         </is>
       </c>
-      <c r="B62" s="56" t="n">
+      <c r="B62" s="57" t="n">
         <v>327.5</v>
       </c>
-      <c r="I62" s="57" t="inlineStr">
+      <c r="I62" s="58" t="inlineStr">
         <is>
           <t>억 엔, 분기 단독(누계 차분), 결산월 다름 — 달력 분기로 맞출 것</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="55" t="inlineStr">
+      <c r="A63" s="56" t="inlineStr">
         <is>
           <t>cons FY28 EPS</t>
         </is>
       </c>
-      <c r="B63" s="56" t="n">
+      <c r="B63" s="57" t="n">
         <v>410.6</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="55" t="inlineStr">
+      <c r="A64" s="56" t="inlineStr">
         <is>
           <t>가격</t>
         </is>
       </c>
-      <c r="B64" s="58" t="n">
+      <c r="B64" s="59" t="n">
         <v>11500</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="55" t="inlineStr">
+      <c r="A65" s="56" t="inlineStr">
         <is>
           <t>mcap</t>
         </is>
       </c>
-      <c r="B65" s="58" t="n">
+      <c r="B65" s="59" t="n">
         <v>16903</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="55" t="inlineStr">
+      <c r="A66" s="56" t="inlineStr">
         <is>
           <t>목표주가 평균</t>
         </is>
       </c>
-      <c r="B66" s="58" t="n">
+      <c r="B66" s="59" t="n">
         <v>9342</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="53" t="inlineStr">
+      <c r="A68" s="54" t="inlineStr">
         <is>
           <t>peers · 9168 라이즈 컨설팅 그룹(2월, IFRS)</t>
         </is>
       </c>
-      <c r="B68" s="53" t="n"/>
-      <c r="C68" s="53" t="n"/>
-      <c r="D68" s="53" t="n"/>
-      <c r="E68" s="53" t="n"/>
-      <c r="F68" s="53" t="n"/>
-      <c r="G68" s="53" t="n"/>
-      <c r="H68" s="53" t="n"/>
-      <c r="I68" s="53" t="n"/>
+      <c r="B68" s="54" t="n"/>
+      <c r="C68" s="54" t="n"/>
+      <c r="D68" s="54" t="n"/>
+      <c r="E68" s="54" t="n"/>
+      <c r="F68" s="54" t="n"/>
+      <c r="G68" s="54" t="n"/>
+      <c r="H68" s="54" t="n"/>
+      <c r="I68" s="54" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="54" t="inlineStr">
+      <c r="A69" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B69" s="54" t="inlineStr">
+      <c r="B69" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="I69" s="54" t="inlineStr">
+      <c r="I69" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="55" t="inlineStr">
+      <c r="A70" s="56" t="inlineStr">
         <is>
           <t>가격</t>
         </is>
       </c>
-      <c r="B70" s="58" t="n">
+      <c r="B70" s="59" t="n">
         <v>360</v>
       </c>
-      <c r="I70" s="57" t="inlineStr">
+      <c r="I70" s="58" t="inlineStr">
         <is>
           <t>억 엔, 분기 단독(누계 차분), 결산월 다름 — 달력 분기로 맞출 것</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="55" t="inlineStr">
+      <c r="A71" s="56" t="inlineStr">
         <is>
           <t>mcap</t>
         </is>
       </c>
-      <c r="B71" s="58" t="n">
+      <c r="B71" s="59" t="n">
         <v>87</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="53" t="inlineStr">
+      <c r="A73" s="54" t="inlineStr">
         <is>
           <t>peers · 6088 시그마크시스 HD(3월, 일본기준)</t>
         </is>
       </c>
-      <c r="B73" s="53" t="n"/>
-      <c r="C73" s="53" t="n"/>
-      <c r="D73" s="53" t="n"/>
-      <c r="E73" s="53" t="n"/>
-      <c r="F73" s="53" t="n"/>
-      <c r="G73" s="53" t="n"/>
-      <c r="H73" s="53" t="n"/>
-      <c r="I73" s="53" t="n"/>
+      <c r="B73" s="54" t="n"/>
+      <c r="C73" s="54" t="n"/>
+      <c r="D73" s="54" t="n"/>
+      <c r="E73" s="54" t="n"/>
+      <c r="F73" s="54" t="n"/>
+      <c r="G73" s="54" t="n"/>
+      <c r="H73" s="54" t="n"/>
+      <c r="I73" s="54" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="54" t="inlineStr">
+      <c r="A74" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B74" s="54" t="inlineStr">
+      <c r="B74" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="I74" s="54" t="inlineStr">
+      <c r="I74" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="55" t="inlineStr">
+      <c r="A75" s="56" t="inlineStr">
         <is>
           <t>가격</t>
         </is>
       </c>
-      <c r="B75" s="58" t="n">
+      <c r="B75" s="59" t="n">
         <v>631</v>
       </c>
-      <c r="I75" s="57" t="inlineStr">
+      <c r="I75" s="58" t="inlineStr">
         <is>
           <t>억 엔, 분기 단독(누계 차분), 결산월 다름 — 달력 분기로 맞출 것</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="55" t="inlineStr">
+      <c r="A76" s="56" t="inlineStr">
         <is>
           <t>mcap</t>
         </is>
       </c>
-      <c r="B76" s="58" t="n">
+      <c r="B76" s="59" t="n">
         <v>508</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="55" t="inlineStr">
+      <c r="A77" s="56" t="inlineStr">
         <is>
           <t>cons FY27 EPS</t>
         </is>
       </c>
-      <c r="B77" s="56" t="n">
+      <c r="B77" s="57" t="n">
         <v>54.9</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="53" t="inlineStr">
+      <c r="A79" s="54" t="inlineStr">
         <is>
           <t>peers · 3697 SHIFT(8월, 일본기준)</t>
         </is>
       </c>
-      <c r="B79" s="53" t="n"/>
-      <c r="C79" s="53" t="n"/>
-      <c r="D79" s="53" t="n"/>
-      <c r="E79" s="53" t="n"/>
-      <c r="F79" s="53" t="n"/>
-      <c r="G79" s="53" t="n"/>
-      <c r="H79" s="53" t="n"/>
-      <c r="I79" s="53" t="n"/>
+      <c r="B79" s="54" t="n"/>
+      <c r="C79" s="54" t="n"/>
+      <c r="D79" s="54" t="n"/>
+      <c r="E79" s="54" t="n"/>
+      <c r="F79" s="54" t="n"/>
+      <c r="G79" s="54" t="n"/>
+      <c r="H79" s="54" t="n"/>
+      <c r="I79" s="54" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="54" t="inlineStr">
+      <c r="A80" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B80" s="54" t="inlineStr">
+      <c r="B80" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="I80" s="54" t="inlineStr">
+      <c r="I80" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="55" t="inlineStr">
+      <c r="A81" s="56" t="inlineStr">
         <is>
           <t>FY27 guide 매출</t>
         </is>
       </c>
-      <c r="B81" s="58" t="n">
+      <c r="B81" s="59" t="n">
         <v>1900</v>
       </c>
-      <c r="I81" s="57" t="inlineStr">
+      <c r="I81" s="58" t="inlineStr">
         <is>
           <t>억 엔, 분기 단독(누계 차분), 결산월 다름 — 달력 분기로 맞출 것</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="55" t="inlineStr">
+      <c r="A82" s="56" t="inlineStr">
         <is>
           <t>가격</t>
         </is>
       </c>
-      <c r="B82" s="58" t="n">
+      <c r="B82" s="59" t="n">
         <v>1156</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="55" t="inlineStr">
+      <c r="A83" s="56" t="inlineStr">
         <is>
           <t>mcap</t>
         </is>
       </c>
-      <c r="B83" s="58" t="n">
+      <c r="B83" s="59" t="n">
         <v>2955</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="55" t="inlineStr">
+      <c r="A84" s="56" t="inlineStr">
         <is>
           <t>cons FY27 EPS</t>
         </is>
       </c>
-      <c r="B84" s="56" t="n">
+      <c r="B84" s="57" t="n">
         <v>54.1</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="53" t="inlineStr">
+      <c r="A86" s="54" t="inlineStr">
         <is>
           <t>annual 실적</t>
         </is>
       </c>
-      <c r="B86" s="53" t="n"/>
-      <c r="C86" s="53" t="n"/>
-      <c r="D86" s="53" t="n"/>
-      <c r="E86" s="53" t="n"/>
-      <c r="F86" s="53" t="n"/>
-      <c r="G86" s="53" t="n"/>
-      <c r="H86" s="53" t="n"/>
-      <c r="I86" s="53" t="n"/>
+      <c r="B86" s="54" t="n"/>
+      <c r="C86" s="54" t="n"/>
+      <c r="D86" s="54" t="n"/>
+      <c r="E86" s="54" t="n"/>
+      <c r="F86" s="54" t="n"/>
+      <c r="G86" s="54" t="n"/>
+      <c r="H86" s="54" t="n"/>
+      <c r="I86" s="54" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="54" t="inlineStr">
+      <c r="A87" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B87" s="54" t="inlineStr">
+      <c r="B87" s="55" t="inlineStr">
         <is>
           <t>span</t>
         </is>
       </c>
-      <c r="C87" s="54" t="inlineStr">
+      <c r="C87" s="55" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="D87" s="54" t="inlineStr">
+      <c r="D87" s="55" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
       </c>
-      <c r="E87" s="54" t="inlineStr">
+      <c r="E87" s="55" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I87" s="54" t="inlineStr">
+      <c r="I87" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="55" t="inlineStr">
+      <c r="A88" s="56" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="B88" s="59" t="inlineStr">
+      <c r="B88" s="60" t="inlineStr">
         <is>
           <t>23.2~24.1</t>
         </is>
       </c>
-      <c r="C88" s="56" t="n">
+      <c r="C88" s="57" t="n">
         <v>91.5</v>
       </c>
-      <c r="D88" s="56" t="n">
+      <c r="D88" s="57" t="n">
         <v>10.9</v>
       </c>
-      <c r="E88" s="59" t="inlineStr">
+      <c r="E88" s="60" t="inlineStr">
         <is>
           <t>FY25 결산단신 증감률로 역산(계산: 164.17/1.795, 27.74/2.537) — 유가증권신고서로 확인 필요</t>
         </is>
       </c>
-      <c r="I88" s="57" t="inlineStr">
+      <c r="I88" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="55" t="inlineStr">
+      <c r="A89" s="56" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="B89" s="59" t="inlineStr">
+      <c r="B89" s="60" t="inlineStr">
         <is>
           <t>24.2~25.1</t>
         </is>
       </c>
-      <c r="C89" s="56" t="n">
+      <c r="C89" s="57" t="n">
         <v>164.17</v>
       </c>
-      <c r="D89" s="56" t="n">
+      <c r="D89" s="57" t="n">
         <v>27.74</v>
       </c>
-      <c r="E89" s="59" t="n"/>
+      <c r="E89" s="60" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="55" t="inlineStr">
+      <c r="A90" s="56" t="inlineStr">
         <is>
           <t>FY2026</t>
         </is>
       </c>
-      <c r="B90" s="59" t="inlineStr">
+      <c r="B90" s="60" t="inlineStr">
         <is>
           <t>25.2~26.1</t>
         </is>
       </c>
-      <c r="C90" s="56" t="n">
+      <c r="C90" s="57" t="n">
         <v>261.85</v>
       </c>
-      <c r="D90" s="56" t="n">
+      <c r="D90" s="57" t="n">
         <v>55.47</v>
       </c>
-      <c r="E90" s="59" t="n"/>
+      <c r="E90" s="60" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="53" t="inlineStr">
+      <c r="A92" s="54" t="inlineStr">
         <is>
           <t>quarterly 실적</t>
         </is>
       </c>
-      <c r="B92" s="53" t="n"/>
-      <c r="C92" s="53" t="n"/>
-      <c r="D92" s="53" t="n"/>
-      <c r="E92" s="53" t="n"/>
-      <c r="F92" s="53" t="n"/>
-      <c r="G92" s="53" t="n"/>
-      <c r="H92" s="53" t="n"/>
-      <c r="I92" s="53" t="n"/>
+      <c r="B92" s="54" t="n"/>
+      <c r="C92" s="54" t="n"/>
+      <c r="D92" s="54" t="n"/>
+      <c r="E92" s="54" t="n"/>
+      <c r="F92" s="54" t="n"/>
+      <c r="G92" s="54" t="n"/>
+      <c r="H92" s="54" t="n"/>
+      <c r="I92" s="54" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="54" t="inlineStr">
+      <c r="A93" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B93" s="54" t="inlineStr">
+      <c r="B93" s="55" t="inlineStr">
         <is>
           <t>span</t>
         </is>
       </c>
-      <c r="C93" s="54" t="inlineStr">
+      <c r="C93" s="55" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="D93" s="54" t="inlineStr">
+      <c r="D93" s="55" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
       </c>
-      <c r="E93" s="54" t="inlineStr">
+      <c r="E93" s="55" t="inlineStr">
         <is>
           <t>ord</t>
         </is>
       </c>
-      <c r="F93" s="54" t="inlineStr">
+      <c r="F93" s="55" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="G93" s="54" t="inlineStr">
+      <c r="G93" s="55" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I93" s="54" t="inlineStr">
+      <c r="I93" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="55" t="inlineStr">
+      <c r="A94" s="56" t="inlineStr">
         <is>
           <t>FY2026-H1</t>
         </is>
       </c>
-      <c r="B94" s="59" t="inlineStr">
+      <c r="B94" s="60" t="inlineStr">
         <is>
           <t>25.2~7</t>
         </is>
       </c>
-      <c r="C94" s="56" t="n">
+      <c r="C94" s="57" t="n">
         <v>115.14</v>
       </c>
-      <c r="D94" s="56" t="n">
+      <c r="D94" s="57" t="n">
         <v>22.33</v>
       </c>
-      <c r="E94" s="56" t="n">
+      <c r="E94" s="57" t="n">
         <v>22.36</v>
       </c>
-      <c r="F94" s="56" t="n">
+      <c r="F94" s="57" t="n">
         <v>15.6</v>
       </c>
-      <c r="G94" s="59" t="inlineStr">
+      <c r="G94" s="60" t="inlineStr">
         <is>
           <t>상장 전이라 1Q·2Q 단독 공시 없음 — 설명회 자료에서 분기 분리 확인 필요</t>
         </is>
       </c>
-      <c r="I94" s="57" t="inlineStr">
+      <c r="I94" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="55" t="inlineStr">
+      <c r="A95" s="56" t="inlineStr">
         <is>
           <t>2026-Q3</t>
         </is>
       </c>
-      <c r="B95" s="59" t="inlineStr">
+      <c r="B95" s="60" t="inlineStr">
         <is>
           <t>25.8~10</t>
         </is>
       </c>
-      <c r="C95" s="56" t="n">
+      <c r="C95" s="57" t="n">
         <v>68.47</v>
       </c>
-      <c r="D95" s="56" t="n">
+      <c r="D95" s="57" t="n">
         <v>14.82</v>
       </c>
-      <c r="E95" s="59" t="n"/>
-      <c r="F95" s="56" t="n">
+      <c r="E95" s="60" t="n"/>
+      <c r="F95" s="57" t="n">
         <v>10.23</v>
       </c>
-      <c r="G95" s="59" t="n"/>
+      <c r="G95" s="60" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="55" t="inlineStr">
+      <c r="A96" s="56" t="inlineStr">
         <is>
           <t>2026-Q4</t>
         </is>
       </c>
-      <c r="B96" s="59" t="inlineStr">
+      <c r="B96" s="60" t="inlineStr">
         <is>
           <t>25.11~26.1</t>
         </is>
       </c>
-      <c r="C96" s="56" t="n">
+      <c r="C96" s="57" t="n">
         <v>78.23999999999999</v>
       </c>
-      <c r="D96" s="56" t="n">
+      <c r="D96" s="57" t="n">
         <v>18.32</v>
       </c>
-      <c r="E96" s="56" t="n">
+      <c r="E96" s="57" t="n">
         <v>17.81</v>
       </c>
-      <c r="F96" s="56" t="n">
+      <c r="F96" s="57" t="n">
         <v>14.63</v>
       </c>
-      <c r="G96" s="59" t="n"/>
+      <c r="G96" s="60" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="55" t="inlineStr">
+      <c r="A97" s="56" t="inlineStr">
         <is>
           <t>2027-Q1</t>
         </is>
       </c>
-      <c r="B97" s="59" t="inlineStr">
+      <c r="B97" s="60" t="inlineStr">
         <is>
           <t>26.2~4</t>
         </is>
       </c>
-      <c r="C97" s="56" t="n">
+      <c r="C97" s="57" t="n">
         <v>88.56</v>
       </c>
-      <c r="D97" s="56" t="n">
+      <c r="D97" s="57" t="n">
         <v>18.09</v>
       </c>
-      <c r="E97" s="56" t="n">
+      <c r="E97" s="57" t="n">
         <v>18.15</v>
       </c>
-      <c r="F97" s="56" t="n">
+      <c r="F97" s="57" t="n">
         <v>13.37</v>
       </c>
-      <c r="G97" s="59" t="n"/>
+      <c r="G97" s="60" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="55" t="inlineStr">
+      <c r="A98" s="56" t="inlineStr">
         <is>
           <t>2027-Q2</t>
         </is>
       </c>
-      <c r="B98" s="59" t="inlineStr">
+      <c r="B98" s="60" t="inlineStr">
         <is>
           <t>26.5~7</t>
         </is>
       </c>
-      <c r="C98" s="56" t="n">
+      <c r="C98" s="57" t="n">
         <v>95.89</v>
       </c>
-      <c r="D98" s="56" t="n">
+      <c r="D98" s="57" t="n">
         <v>19.57</v>
       </c>
-      <c r="E98" s="56" t="n">
+      <c r="E98" s="57" t="n">
         <v>19.58</v>
       </c>
-      <c r="F98" s="56" t="n">
+      <c r="F98" s="57" t="n">
         <v>14.46</v>
       </c>
-      <c r="G98" s="59" t="n"/>
+      <c r="G98" s="60" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="53" t="inlineStr">
+      <c r="A100" s="54" t="inlineStr">
         <is>
           <t>가이던스 path fy2027</t>
         </is>
       </c>
-      <c r="B100" s="53" t="n"/>
-      <c r="C100" s="53" t="n"/>
-      <c r="D100" s="53" t="n"/>
-      <c r="E100" s="53" t="n"/>
-      <c r="F100" s="53" t="n"/>
-      <c r="G100" s="53" t="n"/>
-      <c r="H100" s="53" t="n"/>
-      <c r="I100" s="53" t="n"/>
+      <c r="B100" s="54" t="n"/>
+      <c r="C100" s="54" t="n"/>
+      <c r="D100" s="54" t="n"/>
+      <c r="E100" s="54" t="n"/>
+      <c r="F100" s="54" t="n"/>
+      <c r="G100" s="54" t="n"/>
+      <c r="H100" s="54" t="n"/>
+      <c r="I100" s="54" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="54" t="inlineStr">
+      <c r="A101" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B101" s="54" t="inlineStr">
+      <c r="B101" s="55" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="C101" s="54" t="inlineStr">
+      <c r="C101" s="55" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="D101" s="54" t="inlineStr">
+      <c r="D101" s="55" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
       </c>
-      <c r="E101" s="54" t="inlineStr">
+      <c r="E101" s="55" t="inlineStr">
         <is>
           <t>ord</t>
         </is>
       </c>
-      <c r="F101" s="54" t="inlineStr">
+      <c r="F101" s="55" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="G101" s="54" t="inlineStr">
+      <c r="G101" s="55" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="H101" s="54" t="inlineStr">
+      <c r="H101" s="55" t="inlineStr">
         <is>
           <t>dps</t>
         </is>
       </c>
-      <c r="I101" s="54" t="inlineStr">
+      <c r="I101" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="55" t="inlineStr">
+      <c r="A102" s="56" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="B102" s="59" t="inlineStr">
+      <c r="B102" s="60" t="inlineStr">
         <is>
           <t>최초</t>
         </is>
       </c>
-      <c r="C102" s="56" t="n">
+      <c r="C102" s="57" t="n">
         <v>384.93</v>
       </c>
-      <c r="D102" s="56" t="n">
+      <c r="D102" s="57" t="n">
         <v>86.3</v>
       </c>
-      <c r="E102" s="56" t="n">
+      <c r="E102" s="57" t="n">
         <v>86.47</v>
       </c>
-      <c r="F102" s="56" t="n">
+      <c r="F102" s="57" t="n">
         <v>64.05</v>
       </c>
-      <c r="G102" s="56" t="n">
+      <c r="G102" s="57" t="n">
         <v>92.83</v>
       </c>
-      <c r="H102" s="58" t="n">
+      <c r="H102" s="59" t="n">
         <v>33</v>
       </c>
-      <c r="I102" s="57" t="inlineStr">
+      <c r="I102" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="55" t="inlineStr">
+      <c r="A103" s="56" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B103" s="59" t="inlineStr">
+      <c r="B103" s="60" t="inlineStr">
         <is>
           <t>상향(2Q 발표 때)</t>
         </is>
       </c>
-      <c r="C103" s="56" t="n">
+      <c r="C103" s="57" t="n">
         <v>405.6</v>
       </c>
-      <c r="D103" s="56" t="n">
+      <c r="D103" s="57" t="n">
         <v>92.06999999999999</v>
       </c>
-      <c r="E103" s="56" t="n">
+      <c r="E103" s="57" t="n">
         <v>92.20999999999999</v>
       </c>
-      <c r="F103" s="56" t="n">
+      <c r="F103" s="57" t="n">
         <v>68.23</v>
       </c>
-      <c r="G103" s="56" t="n">
+      <c r="G103" s="57" t="n">
         <v>98.89</v>
       </c>
-      <c r="H103" s="58" t="n">
+      <c r="H103" s="59" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="53" t="inlineStr">
+      <c r="A105" s="54" t="inlineStr">
         <is>
           <t>가이던스 path fy2026</t>
         </is>
       </c>
-      <c r="B105" s="53" t="n"/>
-      <c r="C105" s="53" t="n"/>
-      <c r="D105" s="53" t="n"/>
-      <c r="E105" s="53" t="n"/>
-      <c r="F105" s="53" t="n"/>
-      <c r="G105" s="53" t="n"/>
-      <c r="H105" s="53" t="n"/>
-      <c r="I105" s="53" t="n"/>
+      <c r="B105" s="54" t="n"/>
+      <c r="C105" s="54" t="n"/>
+      <c r="D105" s="54" t="n"/>
+      <c r="E105" s="54" t="n"/>
+      <c r="F105" s="54" t="n"/>
+      <c r="G105" s="54" t="n"/>
+      <c r="H105" s="54" t="n"/>
+      <c r="I105" s="54" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="54" t="inlineStr">
+      <c r="A106" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B106" s="54" t="inlineStr">
+      <c r="B106" s="55" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="C106" s="54" t="inlineStr">
+      <c r="C106" s="55" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I106" s="54" t="inlineStr">
+      <c r="I106" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="55" t="inlineStr">
+      <c r="A107" s="56" t="inlineStr">
         <is>
           <t>2026-01-23</t>
         </is>
       </c>
-      <c r="B107" s="59" t="inlineStr">
+      <c r="B107" s="60" t="inlineStr">
         <is>
           <t>수정 공시</t>
         </is>
       </c>
-      <c r="C107" s="59" t="inlineStr">
+      <c r="C107" s="60" t="inlineStr">
         <is>
           <t>FY26 통기 예상 수정(숫자는 원문 doc 140120260121536455 확인 필요) — 2026-03-13 '예상과 실적 차이' 공시도 있음(doc 140120260313581100)</t>
         </is>
       </c>
-      <c r="I107" s="57" t="inlineStr">
+      <c r="I107" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
@@ -11807,24 +12002,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="60" t="inlineStr">
+      <c r="C3" s="61" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
